--- a/VerveStacks_IND_grids_kan/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_IND_grids_kan/ReportDefs_vervestacks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B56E0341-F974-4E82-BEE7-72529803C937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{828D8638-AECA-426A-8426-9CD81DC6EF55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6694,7 +6694,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58C643C8-72C5-4CF5-A8BE-53E7B0D3D532}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DF51B57-493A-47E4-A896-379F35950BBB}">
   <dimension ref="B9:H527"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -37267,7 +37267,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{583AF7D4-4150-4C51-9E14-DC6241BE583A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D389D56B-B927-475C-BFD8-4A9437C6D9A0}">
   <dimension ref="B9:L527"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_IND_grids_kan/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_IND_grids_kan/ReportDefs_vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{406494FC-F4C6-4DD6-9C6B-094C355964EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C85664CA-4D20-41F4-B8F7-74C4EEEF59AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="geolocation" sheetId="72" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10721" uniqueCount="1958">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10722" uniqueCount="1958">
   <si>
     <t>Unit</t>
   </si>
@@ -52653,6 +52653,9 @@
       <c r="N5" t="s">
         <v>75</v>
       </c>
+      <c r="Q5" t="s">
+        <v>39</v>
+      </c>
       <c r="T5" s="3" t="s">
         <v>39</v>
       </c>

--- a/VerveStacks_IND_grids_kan/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_IND_grids_kan/ReportDefs_vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C85664CA-4D20-41F4-B8F7-74C4EEEF59AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3915B786-5E8D-4550-9DE4-CAD503D1DA6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="geolocation" sheetId="72" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10722" uniqueCount="1958">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10721" uniqueCount="1958">
   <si>
     <t>Unit</t>
   </si>
@@ -52653,9 +52653,6 @@
       <c r="N5" t="s">
         <v>75</v>
       </c>
-      <c r="Q5" t="s">
-        <v>39</v>
-      </c>
       <c r="T5" s="3" t="s">
         <v>39</v>
       </c>

--- a/VerveStacks_IND_grids_kan/ReportDefs_vervestacks.xlsx
+++ b/VerveStacks_IND_grids_kan/ReportDefs_vervestacks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3915B786-5E8D-4550-9DE4-CAD503D1DA6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{225856A3-6BA9-48B3-A75C-7D0F7F0683C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="geolocation" sheetId="72" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10721" uniqueCount="1958">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10755" uniqueCount="1969">
   <si>
     <t>Unit</t>
   </si>
@@ -5929,34 +5929,67 @@
     <t>co2price</t>
   </si>
   <si>
-    <t>base·$000</t>
-  </si>
-  <si>
     <t>base</t>
   </si>
   <si>
-    <t>base·$100</t>
-  </si>
-  <si>
-    <t>base·$200</t>
-  </si>
-  <si>
-    <t>base·$300</t>
-  </si>
-  <si>
-    <t>high·$000</t>
-  </si>
-  <si>
     <t>high</t>
   </si>
   <si>
-    <t>high·$100</t>
-  </si>
-  <si>
-    <t>high·$200</t>
-  </si>
-  <si>
-    <t>high·$300</t>
+    <t>DEF</t>
+  </si>
+  <si>
+    <t>base·$000·Y</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>base·$100·Y</t>
+  </si>
+  <si>
+    <t>base·$200·Y</t>
+  </si>
+  <si>
+    <t>base·$300·Y</t>
+  </si>
+  <si>
+    <t>high·$000·Y</t>
+  </si>
+  <si>
+    <t>high·$100·Y</t>
+  </si>
+  <si>
+    <t>high·$200·Y</t>
+  </si>
+  <si>
+    <t>high·$300·Y</t>
+  </si>
+  <si>
+    <t>base·$000·N</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>base·$100·N</t>
+  </si>
+  <si>
+    <t>base·$200·N</t>
+  </si>
+  <si>
+    <t>base·$300·N</t>
+  </si>
+  <si>
+    <t>high·$000·N</t>
+  </si>
+  <si>
+    <t>high·$100·N</t>
+  </si>
+  <si>
+    <t>high·$200·N</t>
+  </si>
+  <si>
+    <t>high·$300·N</t>
   </si>
 </sst>
 </file>
@@ -52116,7 +52149,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C50B696F-B355-4FC5-AD3E-AFDC509F717D}">
-  <dimension ref="B1:R13"/>
+  <dimension ref="B1:S21"/>
   <sheetFormatPr defaultColWidth="14.73046875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="2.73046875" bestFit="1" customWidth="1"/>
@@ -52140,12 +52173,12 @@
     <col min="24" max="24" width="13.06640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:18">
+    <row r="1" spans="2:19">
       <c r="I1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="2:18">
+    <row r="2" spans="2:19">
       <c r="I2" t="str">
         <f>Q5</f>
         <v>demand</v>
@@ -52154,8 +52187,11 @@
         <f>R5</f>
         <v>co2price</v>
       </c>
-    </row>
-    <row r="4" spans="2:18">
+      <c r="K2" t="s">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="4" spans="2:19">
       <c r="B4" t="s">
         <v>57</v>
       </c>
@@ -52163,7 +52199,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="2:18">
+    <row r="5" spans="2:19">
       <c r="B5" t="s">
         <v>19</v>
       </c>
@@ -52187,6 +52223,10 @@
         <f>"sg_"&amp;J2</f>
         <v>sg_co2price</v>
       </c>
+      <c r="K5" t="str">
+        <f>"sg_"&amp;K2</f>
+        <v>sg_DEF</v>
+      </c>
       <c r="N5" t="s">
         <v>237</v>
       </c>
@@ -52202,19 +52242,22 @@
       <c r="R5" t="s">
         <v>1947</v>
       </c>
-    </row>
-    <row r="6" spans="2:18">
+      <c r="S5" t="s">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="6" spans="2:19">
       <c r="B6" t="str">
         <f>"vs~"&amp;TEXT(P6,"0000")</f>
         <v>vs~0001</v>
       </c>
       <c r="C6" t="str">
         <f>H6</f>
-        <v>base·$000</v>
+        <v>base·$000·Y</v>
       </c>
       <c r="H6" t="str">
         <f>O6</f>
-        <v>base·$000</v>
+        <v>base·$000·Y</v>
       </c>
       <c r="I6" t="str">
         <f>Q6</f>
@@ -52224,279 +52267,687 @@
         <f>TEXT(R6,"$000")</f>
         <v>$000</v>
       </c>
+      <c r="K6" t="str">
+        <f t="shared" ref="K6:K13" si="0">S6</f>
+        <v>Y</v>
+      </c>
       <c r="N6">
         <v>5</v>
       </c>
       <c r="O6" t="s">
-        <v>1948</v>
+        <v>1951</v>
       </c>
       <c r="P6">
         <v>1</v>
       </c>
       <c r="Q6" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="R6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="2:18">
+      <c r="S6" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="7" spans="2:19">
       <c r="B7" t="str">
-        <f t="shared" ref="B7:B13" si="0">"vs~"&amp;TEXT(P7,"0000")</f>
+        <f t="shared" ref="B7:B13" si="1">"vs~"&amp;TEXT(P7,"0000")</f>
         <v>vs~0002</v>
       </c>
       <c r="C7" t="str">
-        <f t="shared" ref="C7:C13" si="1">H7</f>
-        <v>base·$100</v>
+        <f t="shared" ref="C7:C13" si="2">H7</f>
+        <v>base·$100·Y</v>
       </c>
       <c r="H7" t="str">
-        <f t="shared" ref="H7:H13" si="2">O7</f>
-        <v>base·$100</v>
+        <f t="shared" ref="H7:H13" si="3">O7</f>
+        <v>base·$100·Y</v>
       </c>
       <c r="I7" t="str">
-        <f t="shared" ref="I7:I13" si="3">Q7</f>
+        <f t="shared" ref="I7:I13" si="4">Q7</f>
         <v>base</v>
       </c>
       <c r="J7" t="str">
-        <f t="shared" ref="J7:J13" si="4">TEXT(R7,"$000")</f>
+        <f t="shared" ref="J7:J13" si="5">TEXT(R7,"$000")</f>
         <v>$100</v>
+      </c>
+      <c r="K7" t="str">
+        <f t="shared" si="0"/>
+        <v>Y</v>
       </c>
       <c r="N7">
         <v>5</v>
       </c>
       <c r="O7" t="s">
-        <v>1950</v>
+        <v>1953</v>
       </c>
       <c r="P7">
         <v>2</v>
       </c>
       <c r="Q7" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="R7">
         <v>100</v>
       </c>
-    </row>
-    <row r="8" spans="2:18">
+      <c r="S7" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="8" spans="2:19">
       <c r="B8" t="str">
+        <f t="shared" si="1"/>
+        <v>vs~0003</v>
+      </c>
+      <c r="C8" t="str">
+        <f t="shared" si="2"/>
+        <v>base·$200·Y</v>
+      </c>
+      <c r="H8" t="str">
+        <f t="shared" si="3"/>
+        <v>base·$200·Y</v>
+      </c>
+      <c r="I8" t="str">
+        <f t="shared" si="4"/>
+        <v>base</v>
+      </c>
+      <c r="J8" t="str">
+        <f t="shared" si="5"/>
+        <v>$200</v>
+      </c>
+      <c r="K8" t="str">
         <f t="shared" si="0"/>
-        <v>vs~0003</v>
-      </c>
-      <c r="C8" t="str">
-        <f t="shared" si="1"/>
-        <v>base·$200</v>
-      </c>
-      <c r="H8" t="str">
-        <f t="shared" si="2"/>
-        <v>base·$200</v>
-      </c>
-      <c r="I8" t="str">
-        <f t="shared" si="3"/>
-        <v>base</v>
-      </c>
-      <c r="J8" t="str">
-        <f t="shared" si="4"/>
-        <v>$200</v>
+        <v>Y</v>
       </c>
       <c r="N8">
         <v>5</v>
       </c>
       <c r="O8" t="s">
-        <v>1951</v>
+        <v>1954</v>
       </c>
       <c r="P8">
         <v>3</v>
       </c>
       <c r="Q8" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="R8">
         <v>200</v>
       </c>
-    </row>
-    <row r="9" spans="2:18">
+      <c r="S8" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="9" spans="2:19">
       <c r="B9" t="str">
+        <f t="shared" si="1"/>
+        <v>vs~0004</v>
+      </c>
+      <c r="C9" t="str">
+        <f t="shared" si="2"/>
+        <v>base·$300·Y</v>
+      </c>
+      <c r="H9" t="str">
+        <f t="shared" si="3"/>
+        <v>base·$300·Y</v>
+      </c>
+      <c r="I9" t="str">
+        <f t="shared" si="4"/>
+        <v>base</v>
+      </c>
+      <c r="J9" t="str">
+        <f t="shared" si="5"/>
+        <v>$300</v>
+      </c>
+      <c r="K9" t="str">
         <f t="shared" si="0"/>
-        <v>vs~0004</v>
-      </c>
-      <c r="C9" t="str">
-        <f t="shared" si="1"/>
-        <v>base·$300</v>
-      </c>
-      <c r="H9" t="str">
-        <f t="shared" si="2"/>
-        <v>base·$300</v>
-      </c>
-      <c r="I9" t="str">
-        <f t="shared" si="3"/>
-        <v>base</v>
-      </c>
-      <c r="J9" t="str">
-        <f t="shared" si="4"/>
-        <v>$300</v>
+        <v>Y</v>
       </c>
       <c r="N9">
         <v>5</v>
       </c>
       <c r="O9" t="s">
-        <v>1952</v>
+        <v>1955</v>
       </c>
       <c r="P9">
         <v>4</v>
       </c>
       <c r="Q9" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="R9">
         <v>300</v>
       </c>
-    </row>
-    <row r="10" spans="2:18">
+      <c r="S9" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="10" spans="2:19">
       <c r="B10" t="str">
+        <f t="shared" si="1"/>
+        <v>vs~0005</v>
+      </c>
+      <c r="C10" t="str">
+        <f t="shared" si="2"/>
+        <v>high·$000·Y</v>
+      </c>
+      <c r="H10" t="str">
+        <f t="shared" si="3"/>
+        <v>high·$000·Y</v>
+      </c>
+      <c r="I10" t="str">
+        <f t="shared" si="4"/>
+        <v>high</v>
+      </c>
+      <c r="J10" t="str">
+        <f t="shared" si="5"/>
+        <v>$000</v>
+      </c>
+      <c r="K10" t="str">
         <f t="shared" si="0"/>
-        <v>vs~0005</v>
-      </c>
-      <c r="C10" t="str">
-        <f t="shared" si="1"/>
-        <v>high·$000</v>
-      </c>
-      <c r="H10" t="str">
-        <f t="shared" si="2"/>
-        <v>high·$000</v>
-      </c>
-      <c r="I10" t="str">
-        <f t="shared" si="3"/>
-        <v>high</v>
-      </c>
-      <c r="J10" t="str">
-        <f t="shared" si="4"/>
-        <v>$000</v>
+        <v>Y</v>
       </c>
       <c r="N10">
         <v>5</v>
       </c>
       <c r="O10" t="s">
-        <v>1953</v>
+        <v>1956</v>
       </c>
       <c r="P10">
         <v>5</v>
       </c>
       <c r="Q10" t="s">
-        <v>1954</v>
+        <v>1949</v>
       </c>
       <c r="R10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="2:18">
+      <c r="S10" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="11" spans="2:19">
       <c r="B11" t="str">
+        <f t="shared" si="1"/>
+        <v>vs~0006</v>
+      </c>
+      <c r="C11" t="str">
+        <f t="shared" si="2"/>
+        <v>high·$100·Y</v>
+      </c>
+      <c r="H11" t="str">
+        <f t="shared" si="3"/>
+        <v>high·$100·Y</v>
+      </c>
+      <c r="I11" t="str">
+        <f t="shared" si="4"/>
+        <v>high</v>
+      </c>
+      <c r="J11" t="str">
+        <f t="shared" si="5"/>
+        <v>$100</v>
+      </c>
+      <c r="K11" t="str">
         <f t="shared" si="0"/>
-        <v>vs~0006</v>
-      </c>
-      <c r="C11" t="str">
-        <f t="shared" si="1"/>
-        <v>high·$100</v>
-      </c>
-      <c r="H11" t="str">
-        <f t="shared" si="2"/>
-        <v>high·$100</v>
-      </c>
-      <c r="I11" t="str">
-        <f t="shared" si="3"/>
-        <v>high</v>
-      </c>
-      <c r="J11" t="str">
-        <f t="shared" si="4"/>
-        <v>$100</v>
+        <v>Y</v>
       </c>
       <c r="N11">
         <v>5</v>
       </c>
       <c r="O11" t="s">
-        <v>1955</v>
+        <v>1957</v>
       </c>
       <c r="P11">
         <v>6</v>
       </c>
       <c r="Q11" t="s">
-        <v>1954</v>
+        <v>1949</v>
       </c>
       <c r="R11">
         <v>100</v>
       </c>
-    </row>
-    <row r="12" spans="2:18">
+      <c r="S11" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="12" spans="2:19">
       <c r="B12" t="str">
+        <f t="shared" si="1"/>
+        <v>vs~0007</v>
+      </c>
+      <c r="C12" t="str">
+        <f t="shared" si="2"/>
+        <v>high·$200·Y</v>
+      </c>
+      <c r="H12" t="str">
+        <f t="shared" si="3"/>
+        <v>high·$200·Y</v>
+      </c>
+      <c r="I12" t="str">
+        <f t="shared" si="4"/>
+        <v>high</v>
+      </c>
+      <c r="J12" t="str">
+        <f t="shared" si="5"/>
+        <v>$200</v>
+      </c>
+      <c r="K12" t="str">
         <f t="shared" si="0"/>
-        <v>vs~0007</v>
-      </c>
-      <c r="C12" t="str">
-        <f t="shared" si="1"/>
-        <v>high·$200</v>
-      </c>
-      <c r="H12" t="str">
-        <f t="shared" si="2"/>
-        <v>high·$200</v>
-      </c>
-      <c r="I12" t="str">
-        <f t="shared" si="3"/>
-        <v>high</v>
-      </c>
-      <c r="J12" t="str">
-        <f t="shared" si="4"/>
-        <v>$200</v>
+        <v>Y</v>
       </c>
       <c r="N12">
         <v>5</v>
       </c>
       <c r="O12" t="s">
-        <v>1956</v>
+        <v>1958</v>
       </c>
       <c r="P12">
         <v>7</v>
       </c>
       <c r="Q12" t="s">
-        <v>1954</v>
+        <v>1949</v>
       </c>
       <c r="R12">
         <v>200</v>
       </c>
-    </row>
-    <row r="13" spans="2:18">
+      <c r="S12" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="13" spans="2:19">
       <c r="B13" t="str">
+        <f t="shared" si="1"/>
+        <v>vs~0008</v>
+      </c>
+      <c r="C13" t="str">
+        <f t="shared" si="2"/>
+        <v>high·$300·Y</v>
+      </c>
+      <c r="H13" t="str">
+        <f t="shared" si="3"/>
+        <v>high·$300·Y</v>
+      </c>
+      <c r="I13" t="str">
+        <f t="shared" si="4"/>
+        <v>high</v>
+      </c>
+      <c r="J13" t="str">
+        <f t="shared" si="5"/>
+        <v>$300</v>
+      </c>
+      <c r="K13" t="str">
         <f t="shared" si="0"/>
-        <v>vs~0008</v>
-      </c>
-      <c r="C13" t="str">
-        <f t="shared" si="1"/>
-        <v>high·$300</v>
-      </c>
-      <c r="H13" t="str">
-        <f t="shared" si="2"/>
-        <v>high·$300</v>
-      </c>
-      <c r="I13" t="str">
-        <f t="shared" si="3"/>
-        <v>high</v>
-      </c>
-      <c r="J13" t="str">
-        <f t="shared" si="4"/>
-        <v>$300</v>
+        <v>Y</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
       <c r="O13" t="s">
-        <v>1957</v>
+        <v>1959</v>
       </c>
       <c r="P13">
         <v>8</v>
       </c>
       <c r="Q13" t="s">
-        <v>1954</v>
+        <v>1949</v>
       </c>
       <c r="R13">
         <v>300</v>
+      </c>
+      <c r="S13" t="s">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="14" spans="2:19">
+      <c r="B14" t="str">
+        <f t="shared" ref="B14:B21" si="6">"vs~"&amp;TEXT(P14,"0000")</f>
+        <v>vs~0009</v>
+      </c>
+      <c r="C14" t="str">
+        <f t="shared" ref="C14:C21" si="7">H14</f>
+        <v>base·$000·N</v>
+      </c>
+      <c r="H14" t="str">
+        <f t="shared" ref="H14:H21" si="8">O14</f>
+        <v>base·$000·N</v>
+      </c>
+      <c r="I14" t="str">
+        <f t="shared" ref="I14:I21" si="9">Q14</f>
+        <v>base</v>
+      </c>
+      <c r="J14" t="str">
+        <f t="shared" ref="J14:J21" si="10">TEXT(R14,"$000")</f>
+        <v>$000</v>
+      </c>
+      <c r="K14" t="str">
+        <f t="shared" ref="K14:K21" si="11">S14</f>
+        <v>N</v>
+      </c>
+      <c r="N14">
+        <v>5</v>
+      </c>
+      <c r="O14" t="s">
+        <v>1960</v>
+      </c>
+      <c r="P14">
+        <v>9</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>1948</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="15" spans="2:19">
+      <c r="B15" t="str">
+        <f t="shared" si="6"/>
+        <v>vs~0010</v>
+      </c>
+      <c r="C15" t="str">
+        <f t="shared" si="7"/>
+        <v>base·$100·N</v>
+      </c>
+      <c r="H15" t="str">
+        <f t="shared" si="8"/>
+        <v>base·$100·N</v>
+      </c>
+      <c r="I15" t="str">
+        <f t="shared" si="9"/>
+        <v>base</v>
+      </c>
+      <c r="J15" t="str">
+        <f t="shared" si="10"/>
+        <v>$100</v>
+      </c>
+      <c r="K15" t="str">
+        <f t="shared" si="11"/>
+        <v>N</v>
+      </c>
+      <c r="N15">
+        <v>5</v>
+      </c>
+      <c r="O15" t="s">
+        <v>1962</v>
+      </c>
+      <c r="P15">
+        <v>10</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>1948</v>
+      </c>
+      <c r="R15">
+        <v>100</v>
+      </c>
+      <c r="S15" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="16" spans="2:19">
+      <c r="B16" t="str">
+        <f t="shared" si="6"/>
+        <v>vs~0011</v>
+      </c>
+      <c r="C16" t="str">
+        <f t="shared" si="7"/>
+        <v>base·$200·N</v>
+      </c>
+      <c r="H16" t="str">
+        <f t="shared" si="8"/>
+        <v>base·$200·N</v>
+      </c>
+      <c r="I16" t="str">
+        <f t="shared" si="9"/>
+        <v>base</v>
+      </c>
+      <c r="J16" t="str">
+        <f t="shared" si="10"/>
+        <v>$200</v>
+      </c>
+      <c r="K16" t="str">
+        <f t="shared" si="11"/>
+        <v>N</v>
+      </c>
+      <c r="N16">
+        <v>5</v>
+      </c>
+      <c r="O16" t="s">
+        <v>1963</v>
+      </c>
+      <c r="P16">
+        <v>11</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>1948</v>
+      </c>
+      <c r="R16">
+        <v>200</v>
+      </c>
+      <c r="S16" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="17" spans="2:19">
+      <c r="B17" t="str">
+        <f t="shared" si="6"/>
+        <v>vs~0012</v>
+      </c>
+      <c r="C17" t="str">
+        <f t="shared" si="7"/>
+        <v>base·$300·N</v>
+      </c>
+      <c r="H17" t="str">
+        <f t="shared" si="8"/>
+        <v>base·$300·N</v>
+      </c>
+      <c r="I17" t="str">
+        <f t="shared" si="9"/>
+        <v>base</v>
+      </c>
+      <c r="J17" t="str">
+        <f t="shared" si="10"/>
+        <v>$300</v>
+      </c>
+      <c r="K17" t="str">
+        <f t="shared" si="11"/>
+        <v>N</v>
+      </c>
+      <c r="N17">
+        <v>5</v>
+      </c>
+      <c r="O17" t="s">
+        <v>1964</v>
+      </c>
+      <c r="P17">
+        <v>12</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>1948</v>
+      </c>
+      <c r="R17">
+        <v>300</v>
+      </c>
+      <c r="S17" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="18" spans="2:19">
+      <c r="B18" t="str">
+        <f t="shared" si="6"/>
+        <v>vs~0013</v>
+      </c>
+      <c r="C18" t="str">
+        <f t="shared" si="7"/>
+        <v>high·$000·N</v>
+      </c>
+      <c r="H18" t="str">
+        <f t="shared" si="8"/>
+        <v>high·$000·N</v>
+      </c>
+      <c r="I18" t="str">
+        <f t="shared" si="9"/>
+        <v>high</v>
+      </c>
+      <c r="J18" t="str">
+        <f t="shared" si="10"/>
+        <v>$000</v>
+      </c>
+      <c r="K18" t="str">
+        <f t="shared" si="11"/>
+        <v>N</v>
+      </c>
+      <c r="N18">
+        <v>5</v>
+      </c>
+      <c r="O18" t="s">
+        <v>1965</v>
+      </c>
+      <c r="P18">
+        <v>13</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>1949</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="19" spans="2:19">
+      <c r="B19" t="str">
+        <f t="shared" si="6"/>
+        <v>vs~0014</v>
+      </c>
+      <c r="C19" t="str">
+        <f t="shared" si="7"/>
+        <v>high·$100·N</v>
+      </c>
+      <c r="H19" t="str">
+        <f t="shared" si="8"/>
+        <v>high·$100·N</v>
+      </c>
+      <c r="I19" t="str">
+        <f t="shared" si="9"/>
+        <v>high</v>
+      </c>
+      <c r="J19" t="str">
+        <f t="shared" si="10"/>
+        <v>$100</v>
+      </c>
+      <c r="K19" t="str">
+        <f t="shared" si="11"/>
+        <v>N</v>
+      </c>
+      <c r="N19">
+        <v>5</v>
+      </c>
+      <c r="O19" t="s">
+        <v>1966</v>
+      </c>
+      <c r="P19">
+        <v>14</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>1949</v>
+      </c>
+      <c r="R19">
+        <v>100</v>
+      </c>
+      <c r="S19" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="20" spans="2:19">
+      <c r="B20" t="str">
+        <f t="shared" si="6"/>
+        <v>vs~0015</v>
+      </c>
+      <c r="C20" t="str">
+        <f t="shared" si="7"/>
+        <v>high·$200·N</v>
+      </c>
+      <c r="H20" t="str">
+        <f t="shared" si="8"/>
+        <v>high·$200·N</v>
+      </c>
+      <c r="I20" t="str">
+        <f t="shared" si="9"/>
+        <v>high</v>
+      </c>
+      <c r="J20" t="str">
+        <f t="shared" si="10"/>
+        <v>$200</v>
+      </c>
+      <c r="K20" t="str">
+        <f t="shared" si="11"/>
+        <v>N</v>
+      </c>
+      <c r="N20">
+        <v>5</v>
+      </c>
+      <c r="O20" t="s">
+        <v>1967</v>
+      </c>
+      <c r="P20">
+        <v>15</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>1949</v>
+      </c>
+      <c r="R20">
+        <v>200</v>
+      </c>
+      <c r="S20" t="s">
+        <v>1961</v>
+      </c>
+    </row>
+    <row r="21" spans="2:19">
+      <c r="B21" t="str">
+        <f t="shared" si="6"/>
+        <v>vs~0016</v>
+      </c>
+      <c r="C21" t="str">
+        <f t="shared" si="7"/>
+        <v>high·$300·N</v>
+      </c>
+      <c r="H21" t="str">
+        <f t="shared" si="8"/>
+        <v>high·$300·N</v>
+      </c>
+      <c r="I21" t="str">
+        <f t="shared" si="9"/>
+        <v>high</v>
+      </c>
+      <c r="J21" t="str">
+        <f t="shared" si="10"/>
+        <v>$300</v>
+      </c>
+      <c r="K21" t="str">
+        <f t="shared" si="11"/>
+        <v>N</v>
+      </c>
+      <c r="N21">
+        <v>5</v>
+      </c>
+      <c r="O21" t="s">
+        <v>1968</v>
+      </c>
+      <c r="P21">
+        <v>16</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>1949</v>
+      </c>
+      <c r="R21">
+        <v>300</v>
+      </c>
+      <c r="S21" t="s">
+        <v>1961</v>
       </c>
     </row>
   </sheetData>
